--- a/PAMF_DIG F2 - monthly2026-07-19.xlsx
+++ b/PAMF_DIG F2 - monthly2026-07-19.xlsx
@@ -706,7 +706,7 @@
         <v>0.09</v>
       </c>
       <c r="N4" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>0.09</v>
       </c>
       <c r="N5" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
         <v>0.09</v>
       </c>
       <c r="N6" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -998,7 +998,7 @@
         <v>0.09</v>
       </c>
       <c r="N8" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O8" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>0.09</v>
       </c>
       <c r="N9" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O9" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         <v>0.09</v>
       </c>
       <c r="N10" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O10" t="inlineStr">
         <is>
@@ -1217,7 +1217,7 @@
         <v>0.09</v>
       </c>
       <c r="N11" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O11" t="inlineStr">
         <is>
@@ -1363,7 +1363,7 @@
         <v>0.09</v>
       </c>
       <c r="N13" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O13" t="inlineStr">
         <is>
@@ -1436,7 +1436,7 @@
         <v>0.09</v>
       </c>
       <c r="N14" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O14" t="inlineStr">
         <is>
@@ -1509,7 +1509,7 @@
         <v>0.09</v>
       </c>
       <c r="N15" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O15" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>0.09</v>
       </c>
       <c r="N16" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O16" t="inlineStr">
         <is>
@@ -1728,7 +1728,7 @@
         <v>0.09</v>
       </c>
       <c r="N18" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O18" t="inlineStr">
         <is>
@@ -1801,7 +1801,7 @@
         <v>0.09</v>
       </c>
       <c r="N19" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O19" t="inlineStr">
         <is>
@@ -1874,7 +1874,7 @@
         <v>0.09</v>
       </c>
       <c r="N20" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O20" t="inlineStr">
         <is>
@@ -2312,7 +2312,7 @@
         <v>0.09</v>
       </c>
       <c r="N26" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O26" t="inlineStr">
         <is>
@@ -2385,7 +2385,7 @@
         <v>0.09</v>
       </c>
       <c r="N27" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
@@ -2531,7 +2531,7 @@
         <v>0.09</v>
       </c>
       <c r="N29" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O29" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
         <v>0.09</v>
       </c>
       <c r="N31" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O31" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>0.09</v>
       </c>
       <c r="N35" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
@@ -3115,7 +3115,7 @@
         <v>0.09</v>
       </c>
       <c r="N37" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
@@ -3334,7 +3334,7 @@
         <v>0.09</v>
       </c>
       <c r="N40" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O40" t="inlineStr">
         <is>
@@ -3626,7 +3626,7 @@
         <v>0.09</v>
       </c>
       <c r="N44" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O44" t="inlineStr">
         <is>
@@ -3699,7 +3699,7 @@
         <v>0.09</v>
       </c>
       <c r="N45" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O45" t="inlineStr">
         <is>
@@ -3845,7 +3845,7 @@
         <v>0.09</v>
       </c>
       <c r="N47" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O47" t="inlineStr">
         <is>
@@ -3918,7 +3918,7 @@
         <v>0.09</v>
       </c>
       <c r="N48" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O48" t="inlineStr">
         <is>
@@ -4064,7 +4064,7 @@
         <v>0.09</v>
       </c>
       <c r="N50" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
@@ -4210,7 +4210,7 @@
         <v>0.09</v>
       </c>
       <c r="N52" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
@@ -4283,7 +4283,7 @@
         <v>0.09</v>
       </c>
       <c r="N53" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
@@ -4648,7 +4648,7 @@
         <v>0.09</v>
       </c>
       <c r="N58" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
@@ -4721,7 +4721,7 @@
         <v>0.09</v>
       </c>
       <c r="N59" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
@@ -5743,7 +5743,7 @@
         <v>0.09</v>
       </c>
       <c r="N73" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
@@ -6181,7 +6181,7 @@
         <v>0.09</v>
       </c>
       <c r="N79" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O79" t="inlineStr">
         <is>
@@ -6473,7 +6473,7 @@
         <v>0.09</v>
       </c>
       <c r="N83" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O83" t="inlineStr">
         <is>
@@ -6619,7 +6619,7 @@
         <v>0.09</v>
       </c>
       <c r="N85" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O85" t="inlineStr">
         <is>
@@ -6692,7 +6692,7 @@
         <v>0.09</v>
       </c>
       <c r="N86" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O86" t="inlineStr">
         <is>
@@ -6765,7 +6765,7 @@
         <v>0.09</v>
       </c>
       <c r="N87" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O87" t="inlineStr">
         <is>
@@ -6838,7 +6838,7 @@
         <v>0.09</v>
       </c>
       <c r="N88" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O88" t="inlineStr">
         <is>
@@ -7203,7 +7203,7 @@
         <v>0.09</v>
       </c>
       <c r="N93" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O93" t="inlineStr">
         <is>
@@ -7422,7 +7422,7 @@
         <v>0.09</v>
       </c>
       <c r="N96" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O96" t="inlineStr">
         <is>
@@ -7860,7 +7860,7 @@
         <v>0.09</v>
       </c>
       <c r="N102" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O102" t="inlineStr">
         <is>
@@ -8225,7 +8225,7 @@
         <v>0.09</v>
       </c>
       <c r="N107" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O107" t="inlineStr">
         <is>
@@ -8298,7 +8298,7 @@
         <v>0.09</v>
       </c>
       <c r="N108" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O108" t="inlineStr">
         <is>
@@ -8444,7 +8444,7 @@
         <v>0.09</v>
       </c>
       <c r="N110" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O110" t="inlineStr">
         <is>
@@ -8809,7 +8809,7 @@
         <v>0.09</v>
       </c>
       <c r="N115" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O115" t="inlineStr">
         <is>
@@ -9247,7 +9247,7 @@
         <v>0.09</v>
       </c>
       <c r="N121" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O121" t="inlineStr">
         <is>
@@ -9466,7 +9466,7 @@
         <v>0.09</v>
       </c>
       <c r="N124" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O124" t="inlineStr">
         <is>
@@ -9685,7 +9685,7 @@
         <v>0.09</v>
       </c>
       <c r="N127" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O127" t="inlineStr">
         <is>
@@ -9977,7 +9977,7 @@
         <v>0.09</v>
       </c>
       <c r="N131" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O131" t="inlineStr">
         <is>
@@ -10196,7 +10196,7 @@
         <v>0.09</v>
       </c>
       <c r="N134" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O134" t="inlineStr">
         <is>
@@ -10342,7 +10342,7 @@
         <v>0.09</v>
       </c>
       <c r="N136" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O136" t="inlineStr">
         <is>
@@ -10415,7 +10415,7 @@
         <v>0.09</v>
       </c>
       <c r="N137" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O137" t="inlineStr">
         <is>
@@ -10488,7 +10488,7 @@
         <v>0.09</v>
       </c>
       <c r="N138" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O138" t="inlineStr">
         <is>
@@ -10926,7 +10926,7 @@
         <v>0.09</v>
       </c>
       <c r="N144" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O144" t="inlineStr">
         <is>

--- a/PAMF_DIG F2 - monthly2026-07-19.xlsx
+++ b/PAMF_DIG F2 - monthly2026-07-19.xlsx
@@ -3188,7 +3188,7 @@
         <v>0.09</v>
       </c>
       <c r="N38" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
@@ -5816,7 +5816,7 @@
         <v>0.09</v>
       </c>
       <c r="N74" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O74" t="inlineStr">
         <is>
@@ -5962,7 +5962,7 @@
         <v>0.09</v>
       </c>
       <c r="N76" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O76" t="inlineStr">
         <is>
@@ -6327,7 +6327,7 @@
         <v>0.09</v>
       </c>
       <c r="N81" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
@@ -7057,7 +7057,7 @@
         <v>0.09</v>
       </c>
       <c r="N91" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O91" t="inlineStr">
         <is>
@@ -8663,7 +8663,7 @@
         <v>0.09</v>
       </c>
       <c r="N113" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O113" t="inlineStr">
         <is>
@@ -8882,7 +8882,7 @@
         <v>0.09</v>
       </c>
       <c r="N116" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O116" t="inlineStr">
         <is>
@@ -9101,7 +9101,7 @@
         <v>0.09</v>
       </c>
       <c r="N119" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O119" t="inlineStr">
         <is>
@@ -9539,7 +9539,7 @@
         <v>0.09</v>
       </c>
       <c r="N125" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O125" t="inlineStr">
         <is>
@@ -10269,7 +10269,7 @@
         <v>0.09</v>
       </c>
       <c r="N135" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O135" t="inlineStr">
         <is>
@@ -10707,7 +10707,7 @@
         <v>0.09</v>
       </c>
       <c r="N141" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="O141" t="inlineStr">
         <is>
